--- a/data/SR/MV_VE_SR.xlsx
+++ b/data/SR/MV_VE_SR.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hmx/Documents/GitHub/RSV_3seasons_MV/data/SR/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{915F8C1E-CD71-1B49-800E-3D6E4BC7A944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84A5F8A-F278-FA4A-B474-CF773455031E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4700" yWindow="21600" windowWidth="25600" windowHeight="16000" xr2:uid="{E47CEDDB-A67C-4D4E-B46F-EB22E9817989}"/>
+    <workbookView xWindow="4700" yWindow="22100" windowWidth="25600" windowHeight="15500" xr2:uid="{E47CEDDB-A67C-4D4E-B46F-EB22E9817989}"/>
   </bookViews>
   <sheets>
     <sheet name="research studies" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="132">
   <si>
     <t>title</t>
   </si>
@@ -72,9 +72,6 @@
     <t>dta_collect_end</t>
   </si>
   <si>
-    <t>trial</t>
-  </si>
-  <si>
     <t>Bivalent Prefusion F Vaccine in Pregnancy to Prevent RSV Illness in Infants</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>phase III trial (MATISSE)</t>
   </si>
   <si>
-    <t>multi-country</t>
-  </si>
-  <si>
     <t>age_ub_month</t>
   </si>
   <si>
@@ -105,9 +99,6 @@
     <t>studyid</t>
   </si>
   <si>
-    <t>Kampmann et al. 2023</t>
-  </si>
-  <si>
     <t>MA severe RSV LRTI</t>
   </si>
   <si>
@@ -165,9 +156,6 @@
     <t>Argentina BERNI study</t>
   </si>
   <si>
-    <t>Williams et al, 2025</t>
-  </si>
-  <si>
     <t>Bivalent prefusion F vaccination in pregnancy and respiratory syncytial virus hospitalisation in infants in the UK: results of a multicentre, test-negative, case-control study</t>
   </si>
   <si>
@@ -219,9 +207,6 @@
     <t>NVSN (CDC)</t>
   </si>
   <si>
-    <t>Simões et al. 2022</t>
-  </si>
-  <si>
     <t>Prefusion F Protein–Based Respiratory Syncytial Virus Immunization in Pregnancy</t>
   </si>
   <si>
@@ -255,9 +240,6 @@
     <t>Vaccine effectiveness of the maternal RSVpre-F vaccine against severe disease in infants in Scotland, UK: national population-based case-control and cohort analyses</t>
   </si>
   <si>
-    <t>McLachlan et al. 2025</t>
-  </si>
-  <si>
     <t>RSV-associated LRTI hospitalization</t>
   </si>
   <si>
@@ -297,9 +279,6 @@
     <t>RSV-associated ALRI PICU admission</t>
   </si>
   <si>
-    <t>Gentile et al. 2025</t>
-  </si>
-  <si>
     <t>Maternal immunization with RSVpreF vaccine: Effectiveness in preventing respiratory syncytial virus-associated hospitalizations in infants under 6 months in Argentina: Multicenter case-control study</t>
   </si>
   <si>
@@ -390,9 +369,6 @@
     <t>US study</t>
   </si>
   <si>
-    <t>Pérez Marc et al. 2025</t>
-  </si>
-  <si>
     <t>select</t>
   </si>
   <si>
@@ -405,28 +381,58 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/41341162/</t>
   </si>
   <si>
-    <t>Scruzzi et al. 2025</t>
-  </si>
-  <si>
     <t>Evaluation of the effectiveness of the respiratory syncytial virus vaccine in children under 6 months of age in Córdoba, Argentina</t>
   </si>
   <si>
     <t>https://pubmed.ncbi.nlm.nih.gov/40956131/</t>
   </si>
   <si>
-    <t>RSV hospitalization</t>
-  </si>
-  <si>
     <t>relaxed definition</t>
   </si>
   <si>
-    <t>Moline et al. 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabagi et al. 2026 </t>
-  </si>
-  <si>
     <t>Rick et al. 2026</t>
+  </si>
+  <si>
+    <t>RSV illness</t>
+  </si>
+  <si>
+    <t>they just said RSV illness, not sure if this is hospitalization or just infection, but probably not hospitalization according a review included this study, they just labeled as "RSV illness"</t>
+  </si>
+  <si>
+    <t>Clinical trial</t>
+  </si>
+  <si>
+    <t>Multi-country</t>
+  </si>
+  <si>
+    <t>Kampmann et al. 2023 [2]</t>
+  </si>
+  <si>
+    <t>Pérez Marc et al. 2025 [6]</t>
+  </si>
+  <si>
+    <t>Williams et al, 2025 [3]</t>
+  </si>
+  <si>
+    <t>McLachlan et al. 2025 [4]</t>
+  </si>
+  <si>
+    <t>Moline et al. 2025 [5]</t>
+  </si>
+  <si>
+    <t>Jabagi et al. 2026 [11]</t>
+  </si>
+  <si>
+    <t>Simões et al. 2022 [10]</t>
+  </si>
+  <si>
+    <t>Gentile et al. 2025 [14]</t>
+  </si>
+  <si>
+    <t>Razzini et al. 2025 [12]</t>
+  </si>
+  <si>
+    <t>Scruzzi et al. 2025 [13]</t>
   </si>
 </sst>
 </file>
@@ -529,7 +535,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
@@ -568,6 +574,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -898,7 +905,7 @@
   <sheetData>
     <row r="1" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>2</v>
@@ -919,16 +926,16 @@
         <v>10</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>5</v>
@@ -943,30 +950,30 @@
         <v>8</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" s="10" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F2" s="3">
         <v>43709</v>
@@ -978,16 +985,16 @@
         <v>6</v>
       </c>
       <c r="I2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J2" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="M2">
         <v>84.7</v>
@@ -999,27 +1006,27 @@
         <v>97.6</v>
       </c>
       <c r="P2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Q2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E3" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F3" s="3">
         <v>43709</v>
@@ -1031,16 +1038,16 @@
         <v>6</v>
       </c>
       <c r="I3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="L3" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="M3">
         <v>91.5</v>
@@ -1052,27 +1059,27 @@
         <v>99.8</v>
       </c>
       <c r="P3" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="Q3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F4" s="3">
         <v>43999</v>
@@ -1084,16 +1091,16 @@
         <v>3</v>
       </c>
       <c r="I4" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" t="s">
         <v>17</v>
-      </c>
-      <c r="J4" t="s">
-        <v>19</v>
       </c>
       <c r="K4" s="5">
         <v>14</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M4">
         <v>81.8</v>
@@ -1105,30 +1112,30 @@
         <v>96.3</v>
       </c>
       <c r="P4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q4" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B5" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F5" s="3">
         <v>43999</v>
@@ -1140,16 +1147,16 @@
         <v>4</v>
       </c>
       <c r="I5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
         <v>17</v>
-      </c>
-      <c r="J5" t="s">
-        <v>19</v>
       </c>
       <c r="K5" s="5">
         <v>14</v>
       </c>
       <c r="L5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M5">
         <v>73.900000000000006</v>
@@ -1161,27 +1168,27 @@
         <v>88.8</v>
       </c>
       <c r="P5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B6" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F6" s="3">
         <v>43999</v>
@@ -1193,16 +1200,16 @@
         <v>5</v>
       </c>
       <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
         <v>17</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
       </c>
       <c r="K6" s="5">
         <v>14</v>
       </c>
       <c r="L6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M6">
         <v>70.900000000000006</v>
@@ -1214,27 +1221,27 @@
         <v>85.9</v>
       </c>
       <c r="P6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R6" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F7" s="3">
         <v>43999</v>
@@ -1246,16 +1253,16 @@
         <v>6</v>
       </c>
       <c r="I7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J7" t="s">
         <v>17</v>
-      </c>
-      <c r="J7" t="s">
-        <v>19</v>
       </c>
       <c r="K7" s="5">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="M7">
         <v>69.400000000000006</v>
@@ -1267,30 +1274,30 @@
         <v>84.1</v>
       </c>
       <c r="P7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q7" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B8" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F8" s="3">
         <v>43999</v>
@@ -1302,16 +1309,16 @@
         <v>3</v>
       </c>
       <c r="I8" t="s">
+        <v>15</v>
+      </c>
+      <c r="J8" t="s">
         <v>17</v>
-      </c>
-      <c r="J8" t="s">
-        <v>19</v>
       </c>
       <c r="K8" s="5">
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M8">
         <v>57.1</v>
@@ -1323,30 +1330,30 @@
         <v>79.8</v>
       </c>
       <c r="P8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B9" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F9" s="3">
         <v>43999</v>
@@ -1358,16 +1365,16 @@
         <v>4</v>
       </c>
       <c r="I9" t="s">
+        <v>15</v>
+      </c>
+      <c r="J9" t="s">
         <v>17</v>
-      </c>
-      <c r="J9" t="s">
-        <v>19</v>
       </c>
       <c r="K9" s="5">
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M9">
         <v>56.8</v>
@@ -1379,27 +1386,27 @@
         <v>73.5</v>
       </c>
       <c r="P9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="21" t="s">
-        <v>13</v>
-      </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F10" s="3">
         <v>43999</v>
@@ -1411,16 +1418,16 @@
         <v>5</v>
       </c>
       <c r="I10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J10" t="s">
         <v>17</v>
-      </c>
-      <c r="J10" t="s">
-        <v>19</v>
       </c>
       <c r="K10" s="5">
         <v>14</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M10">
         <v>52.5</v>
@@ -1432,27 +1439,27 @@
         <v>68.900000000000006</v>
       </c>
       <c r="P10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B11" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F11" s="3">
         <v>43999</v>
@@ -1464,16 +1471,16 @@
         <v>6</v>
       </c>
       <c r="I11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" t="s">
         <v>17</v>
-      </c>
-      <c r="J11" t="s">
-        <v>19</v>
       </c>
       <c r="K11" s="5">
         <v>14</v>
       </c>
       <c r="L11" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M11">
         <v>51.3</v>
@@ -1485,30 +1492,30 @@
         <v>66.8</v>
       </c>
       <c r="P11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B12" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F12" s="3">
         <v>43999</v>
@@ -1520,16 +1527,16 @@
         <v>3</v>
       </c>
       <c r="I12" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" t="s">
         <v>17</v>
-      </c>
-      <c r="J12" t="s">
-        <v>19</v>
       </c>
       <c r="K12" s="5">
         <v>14</v>
       </c>
       <c r="L12" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M12">
         <v>67.7</v>
@@ -1541,30 +1548,30 @@
         <v>89.5</v>
       </c>
       <c r="P12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B13" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C13" t="s">
         <v>11</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F13" s="3">
         <v>43999</v>
@@ -1576,16 +1583,16 @@
         <v>6</v>
       </c>
       <c r="I13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" t="s">
         <v>17</v>
-      </c>
-      <c r="J13" t="s">
-        <v>19</v>
       </c>
       <c r="K13" s="5">
         <v>14</v>
       </c>
       <c r="L13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M13">
         <v>56.8</v>
@@ -1597,30 +1604,30 @@
         <v>80.7</v>
       </c>
       <c r="P13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q13" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B14" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
         <v>11</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F14" s="3">
         <v>43999</v>
@@ -1632,16 +1639,16 @@
         <v>3</v>
       </c>
       <c r="I14" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" t="s">
         <v>17</v>
-      </c>
-      <c r="J14" t="s">
-        <v>19</v>
       </c>
       <c r="K14" s="5">
         <v>14</v>
       </c>
       <c r="L14" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M14">
         <v>39.1</v>
@@ -1653,30 +1660,30 @@
         <v>55.7</v>
       </c>
       <c r="P14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Q14" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="R14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>122</v>
       </c>
       <c r="B15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" t="s">
         <v>11</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="E15" t="s">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="F15" s="3">
         <v>43999</v>
@@ -1688,16 +1695,16 @@
         <v>6</v>
       </c>
       <c r="I15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" t="s">
         <v>17</v>
-      </c>
-      <c r="J15" t="s">
-        <v>19</v>
       </c>
       <c r="K15" s="5">
         <v>14</v>
       </c>
       <c r="L15" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="M15">
         <v>37.9</v>
@@ -1709,30 +1716,27 @@
         <v>49.5</v>
       </c>
       <c r="P15" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>118</v>
+        <v>13</v>
       </c>
       <c r="R15" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B16" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C16" t="s">
+        <v>31</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" t="s">
         <v>33</v>
-      </c>
-      <c r="C16" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E16" t="s">
-        <v>36</v>
       </c>
       <c r="F16" s="3">
         <v>45383</v>
@@ -1744,16 +1748,16 @@
         <v>3</v>
       </c>
       <c r="I16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K16" s="5">
         <v>14</v>
       </c>
       <c r="L16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M16">
         <v>78.599999999999994</v>
@@ -1765,24 +1769,24 @@
         <v>87.9</v>
       </c>
       <c r="P16" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B17" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" t="s">
-        <v>34</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" t="s">
-        <v>36</v>
       </c>
       <c r="F17" s="3">
         <v>45383</v>
@@ -1794,16 +1798,16 @@
         <v>6</v>
       </c>
       <c r="I17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K17" s="5">
         <v>14</v>
       </c>
       <c r="L17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="M17">
         <v>71.3</v>
@@ -1815,24 +1819,24 @@
         <v>82.3</v>
       </c>
       <c r="P17" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B18" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" t="s">
         <v>33</v>
-      </c>
-      <c r="C18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
       </c>
       <c r="F18" s="3">
         <v>45383</v>
@@ -1844,16 +1848,16 @@
         <v>6</v>
       </c>
       <c r="I18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J18" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K18" s="5">
         <v>14</v>
       </c>
       <c r="L18" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="M18">
         <v>76.900000000000006</v>
@@ -1865,24 +1869,24 @@
         <v>90.3</v>
       </c>
       <c r="P18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D19" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F19" s="3">
         <v>45516</v>
@@ -1894,16 +1898,16 @@
         <v>6</v>
       </c>
       <c r="I19" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K19" s="5">
         <v>0</v>
       </c>
       <c r="L19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M19">
         <v>58</v>
@@ -1915,24 +1919,24 @@
         <v>75</v>
       </c>
       <c r="P19" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F20" s="3">
         <v>45516</v>
@@ -1944,16 +1948,16 @@
         <v>6</v>
       </c>
       <c r="I20" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J20" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K20" s="5">
         <v>14</v>
       </c>
       <c r="L20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M20">
         <v>72</v>
@@ -1965,27 +1969,27 @@
         <v>85</v>
       </c>
       <c r="P20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q20" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F21" s="3">
         <v>45516</v>
@@ -1997,16 +2001,16 @@
         <v>6</v>
       </c>
       <c r="I21" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J21" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K21" s="5">
         <v>14</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M21">
         <v>71</v>
@@ -2018,27 +2022,27 @@
         <v>85</v>
       </c>
       <c r="P21" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q21" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3">
         <v>45516</v>
@@ -2050,16 +2054,16 @@
         <v>6</v>
       </c>
       <c r="I22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J22" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K22" s="5">
         <v>14</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="M22">
         <v>64</v>
@@ -2071,27 +2075,27 @@
         <v>87</v>
       </c>
       <c r="P22" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="Q22" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D23" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F23" s="3">
         <v>45549</v>
@@ -2100,19 +2104,19 @@
         <v>45747</v>
       </c>
       <c r="H23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K23" s="5">
         <v>14</v>
       </c>
       <c r="L23" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="M23">
         <v>54</v>
@@ -2124,24 +2128,24 @@
         <v>67</v>
       </c>
       <c r="P23" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E24" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F24" s="3">
         <v>45549</v>
@@ -2150,19 +2154,19 @@
         <v>45747</v>
       </c>
       <c r="H24" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="I24" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J24" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K24" s="5">
         <v>14</v>
       </c>
       <c r="L24" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M24">
         <v>79</v>
@@ -2174,24 +2178,24 @@
         <v>90</v>
       </c>
       <c r="P24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F25" s="3">
         <v>45566</v>
@@ -2203,16 +2207,16 @@
         <v>6</v>
       </c>
       <c r="I25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="J25" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K25" s="5">
         <v>14</v>
       </c>
       <c r="L25" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M25">
         <v>70</v>
@@ -2224,24 +2228,24 @@
         <v>88</v>
       </c>
       <c r="P25" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C26" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E26" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F26" s="3">
         <v>45516</v>
@@ -2253,16 +2257,16 @@
         <v>3</v>
       </c>
       <c r="I26" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J26" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K26" s="5">
         <v>14</v>
       </c>
       <c r="L26" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M26">
         <v>82.2</v>
@@ -2274,27 +2278,27 @@
         <v>87.3</v>
       </c>
       <c r="P26" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="Q26" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C27" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D27" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F27" s="3">
         <v>45516</v>
@@ -2306,16 +2310,16 @@
         <v>3</v>
       </c>
       <c r="I27" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J27" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K27" s="5">
         <v>14</v>
       </c>
       <c r="L27" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="M27">
         <v>89.9</v>
@@ -2327,24 +2331,24 @@
         <v>97.7</v>
       </c>
       <c r="P27" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C28" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D28" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F28" s="3">
         <v>45516</v>
@@ -2356,16 +2360,16 @@
         <v>3</v>
       </c>
       <c r="I28" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="J28" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="L28" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="M28">
         <v>29.6</v>
@@ -2377,18 +2381,18 @@
         <v>58.6</v>
       </c>
       <c r="P28" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F29" s="3">
         <v>45200</v>
@@ -2400,42 +2404,42 @@
         <v>6</v>
       </c>
       <c r="I29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J29" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K29" s="12">
         <v>0</v>
       </c>
       <c r="L29" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M29">
-        <v>74.2</v>
+        <v>73.900000000000006</v>
       </c>
       <c r="N29">
-        <v>33.6</v>
+        <v>32.799999999999997</v>
       </c>
       <c r="O29">
         <v>92.4</v>
       </c>
-      <c r="P29" t="s">
-        <v>90</v>
+      <c r="P29" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="Q29" s="20" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="17" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F30" s="3">
         <v>45200</v>
@@ -2447,42 +2451,42 @@
         <v>6</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J30" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K30" s="12">
         <v>0</v>
       </c>
       <c r="L30" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M30">
-        <v>85.8</v>
+        <v>86.3</v>
       </c>
       <c r="N30">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="O30">
         <v>99.3</v>
       </c>
-      <c r="P30" t="s">
-        <v>90</v>
+      <c r="P30" s="20" t="s">
+        <v>83</v>
       </c>
       <c r="Q30" s="20" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="18" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F31" s="15">
         <v>45200</v>
@@ -2494,48 +2498,48 @@
         <v>3</v>
       </c>
       <c r="I31" s="13" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K31" s="16">
         <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M31" s="13">
-        <v>76.5</v>
+        <v>76.2</v>
       </c>
       <c r="N31" s="13">
-        <v>31.2</v>
+        <v>30.5</v>
       </c>
       <c r="O31" s="13">
-        <v>94.5</v>
-      </c>
-      <c r="P31" s="13" t="s">
-        <v>90</v>
+        <v>94.4</v>
+      </c>
+      <c r="P31" s="22" t="s">
+        <v>83</v>
       </c>
       <c r="Q31" s="20" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="B32" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E32" t="s">
         <v>33</v>
-      </c>
-      <c r="C32" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" t="s">
-        <v>88</v>
-      </c>
-      <c r="E32" t="s">
-        <v>36</v>
       </c>
       <c r="F32" s="3">
         <v>45366</v>
@@ -2550,7 +2554,7 @@
         <v>14</v>
       </c>
       <c r="L32" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M32">
         <v>78.7</v>
@@ -2562,24 +2566,24 @@
         <v>90.7</v>
       </c>
       <c r="P32" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C33" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F33" s="3">
         <v>45566</v>
@@ -2591,16 +2595,16 @@
         <v>6</v>
       </c>
       <c r="I33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J33" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K33" s="5">
         <v>14</v>
       </c>
       <c r="L33" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="M33">
         <v>64</v>
@@ -2612,24 +2616,24 @@
         <v>79</v>
       </c>
       <c r="P33" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C34" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F34" s="3">
         <v>45566</v>
@@ -2641,16 +2645,16 @@
         <v>6</v>
       </c>
       <c r="I34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="J34" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K34" s="5">
         <v>14</v>
       </c>
       <c r="L34" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M34">
         <v>70</v>
@@ -2662,24 +2666,24 @@
         <v>86</v>
       </c>
       <c r="P34" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C35" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="D35" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="E35" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F35" s="3">
         <v>45536</v>
@@ -2691,7 +2695,7 @@
         <v>5</v>
       </c>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M35">
         <v>50</v>
@@ -2703,24 +2707,24 @@
         <v>55</v>
       </c>
       <c r="P35" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C36" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D36" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E36" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F36" s="3">
         <v>45200</v>
@@ -2732,7 +2736,7 @@
         <v>3</v>
       </c>
       <c r="L36" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M36">
         <v>69</v>
@@ -2744,31 +2748,31 @@
         <v>88</v>
       </c>
       <c r="P36" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="B37" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" t="s">
         <v>33</v>
-      </c>
-      <c r="C37" t="s">
-        <v>120</v>
-      </c>
-      <c r="D37" t="s">
-        <v>121</v>
-      </c>
-      <c r="E37" t="s">
-        <v>36</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37">
         <v>6</v>
       </c>
       <c r="L37" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M37">
         <v>66.099999999999994</v>
@@ -2782,26 +2786,26 @@
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B38" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" t="s">
+        <v>113</v>
+      </c>
+      <c r="E38" t="s">
         <v>33</v>
-      </c>
-      <c r="C38" t="s">
-        <v>120</v>
-      </c>
-      <c r="D38" t="s">
-        <v>121</v>
-      </c>
-      <c r="E38" t="s">
-        <v>36</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38">
         <v>3</v>
       </c>
       <c r="L38" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="M38">
         <v>80.8</v>
@@ -2815,25 +2819,25 @@
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="B39" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C39" t="s">
+        <v>114</v>
+      </c>
+      <c r="D39" t="s">
+        <v>115</v>
+      </c>
+      <c r="E39" t="s">
         <v>33</v>
-      </c>
-      <c r="C39" t="s">
-        <v>123</v>
-      </c>
-      <c r="D39" t="s">
-        <v>124</v>
-      </c>
-      <c r="E39" t="s">
-        <v>36</v>
       </c>
       <c r="H39">
         <v>6</v>
       </c>
       <c r="L39" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="M39">
         <v>74</v>
@@ -2843,6 +2847,9 @@
       </c>
       <c r="O39">
         <v>83</v>
+      </c>
+      <c r="P39" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -2879,7 +2886,7 @@
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>2</v>
@@ -2900,16 +2907,16 @@
         <v>10</v>
       </c>
       <c r="H1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="I1" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>18</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>4</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>5</v>
@@ -2924,48 +2931,48 @@
         <v>8</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H2" t="s">
+        <v>47</v>
+      </c>
+      <c r="I2" t="s">
+        <v>47</v>
+      </c>
+      <c r="J2" t="s">
+        <v>47</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" t="s">
         <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G2" t="s">
-        <v>51</v>
-      </c>
-      <c r="H2" t="s">
-        <v>51</v>
-      </c>
-      <c r="I2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J2" t="s">
-        <v>51</v>
-      </c>
-      <c r="K2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" t="s">
-        <v>69</v>
       </c>
       <c r="M2">
         <v>70</v>
@@ -2977,45 +2984,45 @@
         <v>81</v>
       </c>
       <c r="P2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K3" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="M3">
         <v>56</v>
@@ -3027,45 +3034,45 @@
         <v>69</v>
       </c>
       <c r="P3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="J4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="K4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="M4">
         <v>47</v>
@@ -3077,7 +3084,7 @@
         <v>63</v>
       </c>
       <c r="P4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -3085,59 +3092,59 @@
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
